--- a/Data/EXCEL/Transfer/salemon/202208/8415-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8415-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F1D9DAC-5ED8-47C4-9B19-356346D770F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9621C19B-1644-4B5D-884D-335867D00A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8415-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,21 +1227,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q152"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="5" width="10.125" customWidth="1"/>
-    <col min="6" max="6" width="9.5" customWidth="1"/>
-    <col min="7" max="7" width="11.125" customWidth="1"/>
-    <col min="8" max="8" width="10.125" customWidth="1"/>
-    <col min="9" max="9" width="9.5" customWidth="1"/>
-    <col min="10" max="13" width="10.125" customWidth="1"/>
-    <col min="14" max="14" width="9.5" customWidth="1"/>
-    <col min="15" max="16" width="10.125" customWidth="1"/>
-    <col min="17" max="17" width="10.875" customWidth="1"/>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
+    <col min="8" max="8" width="14.125" customWidth="1"/>
+    <col min="9" max="9" width="13.5" customWidth="1"/>
+    <col min="10" max="13" width="14.125" customWidth="1"/>
+    <col min="14" max="14" width="13.5" customWidth="1"/>
+    <col min="15" max="16" width="14.125" customWidth="1"/>
+    <col min="17" max="17" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1260,7 +1268,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1299,7 +1307,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1342,7 +1350,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1381,7 +1389,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1434,7 +1442,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1487,7 +1495,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1540,7 +1548,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1593,7 +1601,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1646,7 +1654,7 @@
         <v>39.700000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1699,7 +1707,7 @@
         <v>41.3</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1752,7 +1760,7 @@
         <v>43.6</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1805,7 +1813,7 @@
         <v>53.7</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1858,7 +1866,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1911,7 +1919,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1964,7 +1972,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2017,7 +2025,7 @@
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2070,7 +2078,7 @@
         <v>35.799999999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2123,7 +2131,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2176,7 +2184,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2229,7 +2237,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2282,7 +2290,7 @@
         <v>9.83</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2335,7 +2343,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2388,7 +2396,7 @@
         <v>-5.62</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2441,7 +2449,7 @@
         <v>-8.41</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2494,7 +2502,7 @@
         <v>-21.7</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2547,7 +2555,7 @@
         <v>-22.6</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2600,7 +2608,7 @@
         <v>-23.6</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2653,7 +2661,7 @@
         <v>-23.9</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2706,7 +2714,7 @@
         <v>-23.2</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2759,7 +2767,7 @@
         <v>-21.4</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2812,7 +2820,7 @@
         <v>-18.8</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2865,7 +2873,7 @@
         <v>-18.7</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2918,7 +2926,7 @@
         <v>-16.899999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2971,7 +2979,7 @@
         <v>-14.2</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3024,7 +3032,7 @@
         <v>-13.9</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3077,7 +3085,7 @@
         <v>-12.3</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3130,7 +3138,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3183,7 +3191,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3236,7 +3244,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3289,7 +3297,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3342,7 +3350,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3395,7 +3403,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3448,7 +3456,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3501,7 +3509,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3554,7 +3562,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3607,7 +3615,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3660,7 +3668,7 @@
         <v>43.1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3713,7 +3721,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3766,7 +3774,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3819,7 +3827,7 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3872,7 +3880,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3925,7 +3933,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3978,7 +3986,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4031,7 +4039,7 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4084,7 +4092,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4137,7 +4145,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4190,7 +4198,7 @@
         <v>45.1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4243,7 +4251,7 @@
         <v>43.4</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4296,7 +4304,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4349,7 +4357,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4402,7 +4410,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4455,7 +4463,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4508,7 +4516,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4561,7 +4569,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4614,7 +4622,7 @@
         <v>5.72</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4667,7 +4675,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4720,7 +4728,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4773,7 +4781,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4826,7 +4834,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4879,7 +4887,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4932,7 +4940,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4985,7 +4993,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5038,7 +5046,7 @@
         <v>-7.77</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5091,7 +5099,7 @@
         <v>-8.0399999999999991</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5144,7 +5152,7 @@
         <v>-8.5299999999999994</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5197,7 +5205,7 @@
         <v>-8.19</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5250,7 +5258,7 @@
         <v>-7.97</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5303,7 +5311,7 @@
         <v>-8.14</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5356,7 +5364,7 @@
         <v>-6.79</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5409,7 +5417,7 @@
         <v>-7.33</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5462,7 +5470,7 @@
         <v>-8.8800000000000008</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5515,7 +5523,7 @@
         <v>-7.64</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5568,7 +5576,7 @@
         <v>-6.89</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5621,7 +5629,7 @@
         <v>-9.77</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5674,7 +5682,7 @@
         <v>-3.57</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5727,7 +5735,7 @@
         <v>-2.87</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5780,7 +5788,7 @@
         <v>-2.88</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5833,7 +5841,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5886,7 +5894,7 @@
         <v>-2.0499999999999998</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5939,7 +5947,7 @@
         <v>-2.21</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5992,7 +6000,7 @@
         <v>-1.59</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6045,7 +6053,7 @@
         <v>-0.56999999999999995</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6098,7 +6106,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6151,7 +6159,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6204,7 +6212,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6257,7 +6265,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6310,7 +6318,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41944</v>
       </c>
@@ -6363,7 +6371,7 @@
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41913</v>
       </c>
@@ -6416,7 +6424,7 @@
         <v>46.3</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41883</v>
       </c>
@@ -6469,7 +6477,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41852</v>
       </c>
@@ -6522,7 +6530,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41821</v>
       </c>
@@ -6575,7 +6583,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41791</v>
       </c>
@@ -6628,7 +6636,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41760</v>
       </c>
@@ -6681,7 +6689,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41730</v>
       </c>
@@ -6734,7 +6742,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41699</v>
       </c>
@@ -6787,7 +6795,7 @@
         <v>45.9</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41671</v>
       </c>
@@ -6840,7 +6848,7 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41640</v>
       </c>
@@ -6893,7 +6901,7 @@
         <v>41.9</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41609</v>
       </c>
@@ -6946,7 +6954,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41579</v>
       </c>
@@ -6999,7 +7007,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41548</v>
       </c>
@@ -7052,7 +7060,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41518</v>
       </c>
@@ -7105,7 +7113,7 @@
         <v>-1.57</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41487</v>
       </c>
@@ -7158,7 +7166,7 @@
         <v>-1.59</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41456</v>
       </c>
@@ -7211,7 +7219,7 @@
         <v>-0.99</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41426</v>
       </c>
@@ -7264,7 +7272,7 @@
         <v>-2.4</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41395</v>
       </c>
@@ -7317,7 +7325,7 @@
         <v>-2.4300000000000002</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41365</v>
       </c>
@@ -7370,7 +7378,7 @@
         <v>-2.96</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41334</v>
       </c>
@@ -7423,7 +7431,7 @@
         <v>-4.76</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41306</v>
       </c>
@@ -7476,7 +7484,7 @@
         <v>-2.14</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41275</v>
       </c>
@@ -7529,7 +7537,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41244</v>
       </c>
@@ -7582,7 +7590,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41214</v>
       </c>
@@ -7635,7 +7643,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41183</v>
       </c>
@@ -7688,7 +7696,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41153</v>
       </c>
@@ -7741,7 +7749,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>41122</v>
       </c>
@@ -7794,7 +7802,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>41091</v>
       </c>
@@ -7847,7 +7855,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>41061</v>
       </c>
@@ -7900,7 +7908,7 @@
         <v>32.799999999999997</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>41030</v>
       </c>
@@ -7953,7 +7961,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>41000</v>
       </c>
@@ -8006,7 +8014,7 @@
         <v>37.9</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40969</v>
       </c>
@@ -8059,7 +8067,7 @@
         <v>40.200000000000003</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>40940</v>
       </c>
@@ -8112,7 +8120,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="5" customFormat="1">
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>40909</v>
       </c>
@@ -8165,7 +8173,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="5" customFormat="1">
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>40878</v>
       </c>
@@ -8218,7 +8226,7 @@
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="5" customFormat="1">
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>40848</v>
       </c>
@@ -8271,7 +8279,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="135" spans="1:17" s="5" customFormat="1">
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>40817</v>
       </c>
@@ -8324,7 +8332,7 @@
         <v>34.1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="5" customFormat="1">
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>40787</v>
       </c>
@@ -8377,7 +8385,7 @@
         <v>32.799999999999997</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="5" customFormat="1">
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>40756</v>
       </c>
@@ -8430,7 +8438,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="5" customFormat="1">
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>40725</v>
       </c>
@@ -8483,7 +8491,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="139" spans="1:17" s="5" customFormat="1">
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>40695</v>
       </c>
@@ -8536,7 +8544,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="140" spans="1:17" s="5" customFormat="1">
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>40664</v>
       </c>
@@ -8589,7 +8597,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="141" spans="1:17" s="5" customFormat="1">
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>40634</v>
       </c>
@@ -8642,7 +8650,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="142" spans="1:17" s="5" customFormat="1">
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>40603</v>
       </c>
@@ -8695,7 +8703,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:17" s="5" customFormat="1">
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>40575</v>
       </c>
@@ -8748,7 +8756,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" s="5" customFormat="1">
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>40544</v>
       </c>
@@ -8801,7 +8809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="5" customFormat="1">
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>40513</v>
       </c>
@@ -8854,7 +8862,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" s="5" customFormat="1">
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>40483</v>
       </c>
@@ -8907,7 +8915,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="5" customFormat="1">
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>40452</v>
       </c>
@@ -8960,7 +8968,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:17" s="5" customFormat="1">
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>40422</v>
       </c>
@@ -9013,7 +9021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:17" s="5" customFormat="1">
+    <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>40391</v>
       </c>
@@ -9066,7 +9074,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:17" s="5" customFormat="1">
+    <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>40360</v>
       </c>
@@ -9119,7 +9127,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:17" s="5" customFormat="1">
+    <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>40330</v>
       </c>
@@ -9172,7 +9180,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:17" s="5" customFormat="1">
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>40299</v>
       </c>
@@ -9240,7 +9248,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>